--- a/Result/profitability/3268.xlsx
+++ b/Result/profitability/3268.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.34</v>
+        <v>-0.2975</v>
       </c>
       <c r="N2" t="n">
-        <v>7.12625</v>
+        <v>7.235</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3625</v>
+        <v>-0.37875</v>
       </c>
       <c r="N3" t="n">
-        <v>7.603750000000001</v>
+        <v>7.8825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.37875</v>
+        <v>-0.375</v>
       </c>
       <c r="N4" t="n">
-        <v>7.73</v>
+        <v>7.71</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.96</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.49125</v>
+        <v>-0.3325</v>
       </c>
       <c r="N5" t="n">
-        <v>7.06125</v>
+        <v>7.2925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>-0.35</v>
       </c>
       <c r="N6" t="n">
-        <v>7.42</v>
+        <v>7.65375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4075</v>
+        <v>-0.41875</v>
       </c>
       <c r="N7" t="n">
-        <v>7.94</v>
+        <v>7.89875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.39875</v>
+        <v>-0.39125</v>
       </c>
       <c r="N8" t="n">
-        <v>8.231249999999999</v>
+        <v>8.355</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.19375</v>
       </c>
       <c r="N11" t="n">
-        <v>7.351249999999999</v>
+        <v>7.35125</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>301</v>
+      </c>
+      <c r="D75" t="n">
+        <v>279</v>
+      </c>
+      <c r="E75" t="n">
+        <v>22</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.215</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.345</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9900000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9769230769230769</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3419593345656191</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
